--- a/output/2026-09-01_08_Italia_Emilia_Romagna_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-01_08_Italia_Emilia_Romagna_Utensilerie_e_Macchine_Utensili.xlsx
@@ -541,7 +541,6 @@
           <t>051 460082</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Verificata su Virgilio Aziende, Atoka, Misterimprese.</t>
@@ -616,8 +615,6 @@
           <t>Macchine CNC nuove e usate, rivenditore ufficiale marchi lavorazione meccanica</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Fondata 1995 (Cecoli/Bonaga). Telefono/email non reperiti - lasciati vuoti.</t>
@@ -739,7 +736,6 @@
           <t>059 250451</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Fondata 1972; tratta anche sistemi di aspirazione - potenziale sinergia diretta con Dupuy.</t>
@@ -987,10 +983,9 @@
           <t>059 361164</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Indirizzo aggiornato con dato reale reperito: Via Pancaldi 59, 41122 Modena. Attiva dal 1976, opera anche su Bologna e Parma.</t>
+          <t>Indirizzo aggiornato con dato reale reperito: Via Pancaldi 59, 41122 Modena. Attiva dal 1976, opera anche su Bologna e Parma. [DUPLICATO — vedi anche: 2026-08-31_20_Italia_Emilia_Romagna_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1020,8 +1015,6 @@
           <t>Rivendita macchine utensili tradizionali/CNC usate, revisione e manutenzione (torni, rettificatrici, presse)</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>Verificata; opera anche su Modena e nord Italia. Telefono/email non reperiti.</t>
@@ -1059,7 +1052,6 @@
           <t>0522 506261</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>Verificata.</t>
@@ -1097,7 +1089,6 @@
           <t>0522 924221</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>Fondata 1972. Indirizzo verificato: Via Denti Antonio, 1, 42124 Reggio Emilia; telefono aggiornato con dato reale reperito.</t>
@@ -1135,7 +1126,6 @@
           <t>0522 921307</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>Attiva dal 1981. Verificata.</t>
@@ -1168,8 +1158,6 @@
           <t>Utensili elettrici e manuali, strumenti di misura, DPI, arredamento industriale, sollevamento</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>Verificata (P.IVA 01919400349).</t>
@@ -1229,7 +1217,6 @@
           <t>M.U.P. Morani Utensili Parma S.r.l.</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>Parma (PR) - Vigatto</t>
@@ -1245,7 +1232,6 @@
           <t>0521 631155</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>Verificata; nessun sito web ufficiale reperito - lasciato vuoto.</t>
@@ -1283,7 +1269,6 @@
           <t>0523 331252</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>Fondata 1955. Verificata.</t>
@@ -1358,8 +1343,6 @@
           <t>Utensili speciali a disegno alte prestazioni per settori automotive/aerospace</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>Fondata 1954. Verificata; telefono/email non reperiti.</t>
@@ -1392,8 +1375,6 @@
           <t>Portastampi per iniezione materie plastiche e pressofusione leghe leggere, ISO 9001</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>Fondata 1972. Sito web aggiornato con dato reale reperito. Telefono/email non reperiti.</t>
@@ -1431,7 +1412,6 @@
           <t>0523 610105</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>Attiva dal 1986. Verificata.</t>
@@ -1511,7 +1491,6 @@
           <t>0533 94136</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>Verificata; profilo con componente B2B industriale mantenuta in target.</t>
@@ -1717,7 +1696,6 @@
           <t>0543 480333</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>Dati aggiornati con fonte reale.</t>
@@ -1777,7 +1755,6 @@
           <t>Utensileria Romagnola di Randi Marco e C. S.n.c.</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
           <t>Rimini (RN)</t>
@@ -1793,7 +1770,6 @@
           <t>0541 783105</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>Verificata, nessun sito ufficiale reperito - lasciato vuoto.</t>

--- a/output/2026-09-01_08_Italia_Emilia_Romagna_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-01_08_Italia_Emilia_Romagna_Utensilerie_e_Macchine_Utensili.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
